--- a/data/trans_camb/P1408-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1408-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,56</t>
+          <t>-2,63; -0,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,25</t>
+          <t>-2,06; 0,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,57</t>
+          <t>-2,53; -0,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,0</t>
+          <t>-1,04; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,0</t>
+          <t>-1,0; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,18</t>
+          <t>0,26; 6,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; -0,36</t>
+          <t>-1,4; -0,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,03</t>
+          <t>-1,16; 0,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,19</t>
+          <t>-0,65; 2,29</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1166,63%</t>
+          <t>1036,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 97,47</t>
+          <t>-100,0; 232,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,11</t>
+          <t>-100,0; 147,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 498,74</t>
+          <t>-77,1; 680,29</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; -0,25</t>
+          <t>-1,89; -0,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,02</t>
+          <t>-1,77; 0,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,68</t>
+          <t>-1,51; 0,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; -0,7</t>
+          <t>-3,14; -0,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,26</t>
+          <t>-2,66; -0,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,8</t>
+          <t>-2,25; 0,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; -0,7</t>
+          <t>-2,08; -0,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; -0,38</t>
+          <t>-1,81; -0,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,39</t>
+          <t>-1,44; 0,26</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-48,76%</t>
+          <t>-53,65%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-42,19%</t>
+          <t>-40,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-41,69%</t>
+          <t>-43,54%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 11,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 64,44</t>
+          <t>-100,0; 117,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 201,21</t>
+          <t>-100,0; 270,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -7,88</t>
+          <t>-100,0; 6,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,34</t>
+          <t>-97,04; 11,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,81; 82,94</t>
+          <t>-83,7; 88,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -38,35</t>
+          <t>-100,0; -55,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-92,59; -20,41</t>
+          <t>-91,29; -21,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-78,71; 58,68</t>
+          <t>-78,6; 32,83</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-0,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,54</t>
+          <t>-1,43; 0,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,34</t>
+          <t>-1,67; 0,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,37</t>
+          <t>-1,8; 0,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,11</t>
+          <t>-2,19; 0,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,11</t>
+          <t>-2,2; 0,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,04</t>
+          <t>-2,24; 0,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,06</t>
+          <t>-1,35; 0,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; -0,21</t>
+          <t>-1,53; -0,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; -0,13</t>
+          <t>-1,61; -0,18</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-59,75%</t>
+          <t>-62,71%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-59,66%</t>
+          <t>-63,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-59,91%</t>
+          <t>-63,57%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,09; 125,06</t>
+          <t>-85,36; 137,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 119,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,42</t>
+          <t>-100,0; 95,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-91,73; 21,65</t>
+          <t>-89,73; 35,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,02; 34,42</t>
+          <t>-91,76; 36,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,06; 26,25</t>
+          <t>-91,92; 19,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,3; 19,14</t>
+          <t>-77,44; 31,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,78; -6,84</t>
+          <t>-84,83; 4,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,56; 1,01</t>
+          <t>-87,28; -5,02</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-1,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,35</t>
+          <t>-3,55; 0,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,07</t>
+          <t>-3,4; -0,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,35</t>
+          <t>-2,77; 0,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,62</t>
+          <t>-4,05; -0,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,95</t>
+          <t>-4,35; -0,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,34</t>
+          <t>-2,91; 0,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -0,69</t>
+          <t>-3,08; -0,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,99</t>
+          <t>-3,24; -0,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; -0,29</t>
+          <t>-2,38; 0,12</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-48,85%</t>
+          <t>-30,21%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-43,78%</t>
+          <t>-43,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,68%</t>
+          <t>-37,22%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,09; 55,1</t>
+          <t>-88,38; 35,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-86,41; 8,47</t>
+          <t>-84,58; 14,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,42; 20,25</t>
+          <t>-70,41; 68,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-94,6; -9,41</t>
+          <t>-94,53; -14,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-95,0; -28,22</t>
+          <t>-95,51; -40,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 20,75</t>
+          <t>-70,57; 12,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-85,18; -20,89</t>
+          <t>-84,51; -20,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-86,77; -40,65</t>
+          <t>-85,76; -34,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,18; -10,45</t>
+          <t>-64,5; 7,63</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,15</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 0,35</t>
+          <t>-6,03; 0,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,88</t>
+          <t>-5,26; 0,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,99; -0,59</t>
+          <t>-6,08; -0,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,63</t>
+          <t>-2,18; 1,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,78</t>
+          <t>-2,77; 0,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,29</t>
+          <t>-1,29; 2,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,5</t>
+          <t>-3,32; 0,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,38</t>
+          <t>-3,52; 0,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,43</t>
+          <t>-3,01; 0,43</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-49,39%</t>
+          <t>-47,58%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-28,37%</t>
+          <t>-26,66%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-74,25; 9,71</t>
+          <t>-73,3; 8,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,34; 21,24</t>
+          <t>-64,82; 26,89</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,62; -11,82</t>
+          <t>-70,73; -8,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-66,81; 160,59</t>
+          <t>-65,22; 140,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-82,56; 90,28</t>
+          <t>-81,42; 91,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 193,2</t>
+          <t>-37,94; 212,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-61,61; 20,39</t>
+          <t>-62,39; 9,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 13,33</t>
+          <t>-64,86; 6,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-53,41; 14,75</t>
+          <t>-53,92; 11,98</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-3,88</t>
+          <t>-4,12</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,76</t>
+          <t>-2,69</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -0,41</t>
+          <t>-9,3; -0,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,52; -2,32</t>
+          <t>-10,33; -2,47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -0,19</t>
+          <t>-8,46; -0,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,97; -1,64</t>
+          <t>-6,96; -1,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 0,56</t>
+          <t>-5,45; 0,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,85; -0,49</t>
+          <t>-4,45; 0,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -1,97</t>
+          <t>-6,93; -1,88</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -1,83</t>
+          <t>-6,76; -1,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,07; -1,29</t>
+          <t>-5,33; -0,46</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-37,23%</t>
+          <t>-39,49%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-53,06%</t>
+          <t>-26,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-47,5%</t>
+          <t>-33,95%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-72,1; -2,92</t>
+          <t>-70,69; -1,79</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-79,99; -26,93</t>
+          <t>-80,91; -28,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-60,04; -1,51</t>
+          <t>-63,75; -6,03</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-89,15; -27,01</t>
+          <t>-89,18; -27,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-71,92; 18,42</t>
+          <t>-72,03; 23,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-85,94; -11,58</t>
+          <t>-59,77; 25,61</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-72,24; -26,08</t>
+          <t>-74,58; -27,1</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -25,31</t>
+          <t>-70,98; -24,39</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-74,98; -21,59</t>
+          <t>-55,04; -7,23</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-12,9</t>
+          <t>-13,24</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-5,41</t>
+          <t>-5,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-17,26; -4,0</t>
+          <t>-17,18; -3,54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-21,74; -8,69</t>
+          <t>-20,15; -8,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,68; -6,85</t>
+          <t>-19,55; -7,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,87</t>
+          <t>-6,95; 0,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,22</t>
+          <t>-7,33; 0,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,17</t>
+          <t>-4,6; 2,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -2,46</t>
+          <t>-9,4; -2,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -4,38</t>
+          <t>-10,99; -4,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,64; -2,33</t>
+          <t>-9,17; -2,4</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-60,02%</t>
+          <t>-61,61%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-10,27%</t>
+          <t>-11,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-42,41%</t>
+          <t>-43,71%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-68,64; -20,57</t>
+          <t>-66,69; -17,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-80,56; -47,39</t>
+          <t>-79,63; -46,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-73,46; -38,25</t>
+          <t>-74,42; -43,65</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-68,81; 16,35</t>
+          <t>-69,51; 16,3</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-73,83; 5,5</t>
+          <t>-75,79; 5,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-44,95; 46,02</t>
+          <t>-45,88; 46,53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-62,56; -20,19</t>
+          <t>-63,93; -21,32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-73,78; -39,68</t>
+          <t>-73,67; -40,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,73; -21,58</t>
+          <t>-59,06; -22,73</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>-0,86</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,81; -1,05</t>
+          <t>-2,95; -1,17</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -1,33</t>
+          <t>-3,07; -1,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,62; -0,84</t>
+          <t>-2,38; -0,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,26; -0,86</t>
+          <t>-2,12; -0,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,8</t>
+          <t>-2,18; -0,73</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,47</t>
+          <t>-0,91; 0,54</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -1,19</t>
+          <t>-2,37; -1,22</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -1,29</t>
+          <t>-2,36; -1,28</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,33</t>
+          <t>-1,41; -0,32</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-41,68%</t>
+          <t>-38,58%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-10,53%</t>
+          <t>-5,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-29,15%</t>
+          <t>-25,12%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-61,18; -28,96</t>
+          <t>-63,61; -30,64</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-65,19; -36,12</t>
+          <t>-65,26; -38,43</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-56,71; -23,44</t>
+          <t>-51,62; -21,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-70,45; -35,17</t>
+          <t>-68,85; -35,09</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-68,41; -32,66</t>
+          <t>-68,29; -32,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 20,86</t>
+          <t>-29,05; 23,27</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-61,51; -38,14</t>
+          <t>-62,78; -39,34</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-62,47; -40,49</t>
+          <t>-63,3; -41,46</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-42,91; -10,66</t>
+          <t>-38,19; -10,22</t>
         </is>
       </c>
     </row>
